--- a/90_Threshold_OUTPUT_REPORT/90_report_data.xlsx
+++ b/90_Threshold_OUTPUT_REPORT/90_report_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V314"/>
+  <dimension ref="A1:W314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,15 +526,20 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Inverted_Pval</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
@@ -590,7 +595,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3405</v>
+        <v>0.3602</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -620,13 +625,18 @@
           <t>TATCATATGATA</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
         <v>0.02419032387045182</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.9758096761295482</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -682,7 +692,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.1727</v>
+        <v>0.1824</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -712,13 +722,18 @@
           <t>GTATCATATGATAC</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>0.01839264294282287</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.9816073570571772</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -770,7 +785,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.1047</v>
+        <v>0.1095</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -784,15 +799,16 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -842,7 +858,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.0765</v>
+        <v>0.0818</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -856,15 +872,16 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -918,7 +935,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2922</v>
+        <v>0.301</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -948,13 +965,18 @@
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>0.241703318672531</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.758296681327469</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1010,7 +1032,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2922</v>
+        <v>0.301</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1040,13 +1062,18 @@
           <t>CACA</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
         <v>0.1605357856857257</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.8394642143142743</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1102,7 +1129,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.3008</v>
+        <v>0.262</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1132,13 +1159,18 @@
           <t>GTGATCGATATCAC</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1194,7 +1226,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.3008</v>
+        <v>0.262</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1224,13 +1256,18 @@
           <t>TGTGATCGATATCA</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
         <v>0.1681327469012395</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.8318672530987605</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1286,7 +1323,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.3008</v>
+        <v>0.262</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1316,13 +1353,18 @@
           <t>TGATCGATATCACA</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
         <v>0.4978008796481407</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.5021991203518592</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1378,7 +1420,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.1924</v>
+        <v>0.2355</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1408,13 +1450,18 @@
           <t>CACA</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
         <v>0.4226309476209516</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.5773690523790485</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1470,7 +1517,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.238</v>
+        <v>0.1982</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1500,13 +1547,18 @@
           <t>GTGATCAAGATCAC</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -1562,7 +1614,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.238</v>
+        <v>0.1982</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1592,13 +1644,18 @@
           <t>TGATCAAGATCACA</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
         <v>0.5505797680927629</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.4494202319072371</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -1654,7 +1711,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1684,13 +1741,18 @@
           <t>CACCGCACC</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>0.5121951219512195</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.4878048780487805</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1746,7 +1808,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1776,13 +1838,18 @@
           <t>CGCTTCACCGC</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.01239504198320673</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1838,7 +1905,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1868,13 +1935,18 @@
           <t>CGGTGCG</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -1930,7 +2002,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1960,13 +2032,18 @@
           <t>GCGC</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2022,7 +2099,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -2052,13 +2129,18 @@
           <t>ACGGTGCGCTTCAC</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2114,7 +2196,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -2144,13 +2226,18 @@
           <t>CGGTGCGCTTCACCG</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2206,7 +2293,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2236,13 +2323,18 @@
           <t>GCGCTTCACCGC</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2298,7 +2390,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -2328,13 +2420,18 @@
           <t>ACGGTGCGCTTCACCGCAC</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2390,7 +2487,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -2420,13 +2517,18 @@
           <t>CCGCACCC</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2482,7 +2584,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.3785</v>
+        <v>0.4257</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2512,13 +2614,18 @@
           <t>CCC</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -2574,7 +2681,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2604,13 +2711,18 @@
           <t>GGTGCGCTTCACCGCACC</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
         <v>0.01239504198320672</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.9876049580167933</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -2666,7 +2778,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2696,13 +2808,18 @@
           <t>CGGTGCGCTTCACCG</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
         <v>0.08256697321071571</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.9174330267892843</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2758,7 +2875,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2788,13 +2905,18 @@
           <t>ACGGT</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2850,7 +2972,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2880,13 +3002,18 @@
           <t>CGGTGCG</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -2942,7 +3069,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2972,13 +3099,18 @@
           <t>GCGC</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3034,7 +3166,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -3064,13 +3196,18 @@
           <t>AACGGTGCGCTT</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3126,7 +3263,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -3156,13 +3293,18 @@
           <t>GCTTCACCGC</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3218,7 +3360,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.4259</v>
+        <v>0.3632</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -3248,13 +3390,18 @@
           <t>GGTGCGCTTCACCGCACCC</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -3310,7 +3457,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.2483</v>
+        <v>0.2937</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -3340,13 +3487,18 @@
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>0.01679328268692523</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.9832067173130747</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -3398,7 +3550,7 @@
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
-        <v>0.1295</v>
+        <v>0.0809</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -3412,15 +3564,16 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0</v>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3627,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.2676</v>
+        <v>0.3039</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -3504,13 +3657,18 @@
           <t>TCGATC</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
         <v>0.8470611755297881</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -3566,7 +3724,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.2676</v>
+        <v>0.3039</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -3596,13 +3754,18 @@
           <t>CACA</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
         <v>0.8470611755297881</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.1529388244702119</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -3654,7 +3817,7 @@
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>0.1407</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
@@ -3668,15 +3831,16 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="n">
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0</v>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3894,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.1959</v>
+        <v>0.2348</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -3760,13 +3924,18 @@
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>0.07936825269892044</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.9206317473010796</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -3822,7 +3991,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.1959</v>
+        <v>0.2348</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -3852,13 +4021,18 @@
           <t>CACA</t>
         </is>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
         <v>0.03298680527788884</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.9670131947221111</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -3914,7 +4088,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.2575</v>
+        <v>0.2021</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -3944,13 +4118,18 @@
           <t>GTGATCTACATCAC</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
         <v>0.0007996801279488205</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.9992003198720512</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4006,7 +4185,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.2575</v>
+        <v>0.2021</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -4036,13 +4215,18 @@
           <t>TGTGATCTACATCA</t>
         </is>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
         <v>0.1535385845661735</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.8464614154338265</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4098,7 +4282,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.2575</v>
+        <v>0.2021</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -4128,13 +4312,18 @@
           <t>TGATCTACATCACA</t>
         </is>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
         <v>0.1695321871251499</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0.8304678128748501</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4190,7 +4379,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.2815</v>
+        <v>0.3209</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -4220,13 +4409,18 @@
           <t>TGTG</t>
         </is>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>0.07117153138744502</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.928828468612555</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4282,7 +4476,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.3206</v>
+        <v>0.2801</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -4312,13 +4506,18 @@
           <t>GTGATTTAGATCAC</t>
         </is>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -4374,7 +4573,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.3206</v>
+        <v>0.2801</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -4404,13 +4603,18 @@
           <t>TGTGATTTAGATCA</t>
         </is>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>0.3324670131947221</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.667532986805278</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -4466,7 +4670,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -4496,13 +4700,18 @@
           <t>GATTGAT</t>
         </is>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
         <v>0.9960015993602559</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4558,7 +4767,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -4588,13 +4797,18 @@
           <t>GTTAGATTGATCACGTT</t>
         </is>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>0.9960015993602559</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4650,7 +4864,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -4680,13 +4894,18 @@
           <t>GCAAGGTGTTAGATTGATCACGTTTCCAGCA</t>
         </is>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
         <v>0.9960015993602559</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0.003998400639744104</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4742,7 +4961,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -4772,13 +4991,18 @@
           <t>GGCAAGG</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4834,7 +5058,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -4864,13 +5088,18 @@
           <t>GTGT</t>
         </is>
       </c>
-      <c r="T49" t="n">
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -4926,7 +5155,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -4956,13 +5185,18 @@
           <t>AGGTGTTAG</t>
         </is>
       </c>
-      <c r="T50" t="n">
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5018,7 +5252,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -5048,13 +5282,18 @@
           <t>TTAGATT</t>
         </is>
       </c>
-      <c r="T51" t="n">
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5110,7 +5349,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -5140,13 +5379,18 @@
           <t>TGTTAGATTG</t>
         </is>
       </c>
-      <c r="T52" t="n">
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5202,7 +5446,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -5232,13 +5476,18 @@
           <t>CAAGGTGTTAGATTGATCA</t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5294,7 +5543,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -5324,13 +5573,18 @@
           <t>GTGTTAGATTGATCACGT</t>
         </is>
       </c>
-      <c r="T54" t="n">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5386,7 +5640,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -5416,13 +5670,18 @@
           <t>TTGATCACGTT</t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5478,7 +5737,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -5508,13 +5767,18 @@
           <t>TTAGATTGATCACGTTT</t>
         </is>
       </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5570,7 +5834,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -5600,13 +5864,18 @@
           <t>TTGATCACGTTT</t>
         </is>
       </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5662,7 +5931,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -5692,13 +5961,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5754,7 +6028,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -5784,13 +6058,18 @@
           <t>TCACGTTTC</t>
         </is>
       </c>
-      <c r="T59" t="n">
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5846,7 +6125,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -5876,13 +6155,18 @@
           <t>CAAGGTGTTAGATTGATCACGTTTCCA</t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -5938,7 +6222,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -5968,13 +6252,18 @@
           <t>CACGTTTCCA</t>
         </is>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6030,7 +6319,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -6060,13 +6349,18 @@
           <t>AGGTGTTAGATTGATCACGTTTCCAG</t>
         </is>
       </c>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6122,7 +6416,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -6152,13 +6446,18 @@
           <t>AGATTGATCACGTTTCCAG</t>
         </is>
       </c>
-      <c r="T63" t="n">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6214,7 +6513,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -6244,13 +6543,18 @@
           <t>CACGTTTCCAGCA</t>
         </is>
       </c>
-      <c r="T64" t="n">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6306,7 +6610,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.7098</v>
+        <v>0.7118</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -6336,13 +6640,18 @@
           <t>CAGCA</t>
         </is>
       </c>
-      <c r="T65" t="n">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -6398,7 +6707,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -6428,13 +6737,18 @@
           <t>CAAGGTGTTAGATTG</t>
         </is>
       </c>
-      <c r="T66" t="n">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6490,7 +6804,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -6520,13 +6834,18 @@
           <t>GATTGATC</t>
         </is>
       </c>
-      <c r="T67" t="n">
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6582,7 +6901,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -6612,13 +6931,18 @@
           <t>TGATCA</t>
         </is>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6674,7 +6998,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -6704,13 +7028,18 @@
           <t>GTGTTAGATTGATCAC</t>
         </is>
       </c>
-      <c r="T69" t="n">
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
         <v>0.9948020791683326</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.005197920831667369</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6766,7 +7095,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -6796,13 +7125,18 @@
           <t>CAAGGTG</t>
         </is>
       </c>
-      <c r="T70" t="n">
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U70" t="n">
+      <c r="V70" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6858,7 +7192,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -6888,13 +7222,18 @@
           <t>AAGGTGTT</t>
         </is>
       </c>
-      <c r="T71" t="n">
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -6950,7 +7289,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -6980,13 +7319,18 @@
           <t>GTTAGATTGATCAC</t>
         </is>
       </c>
-      <c r="T72" t="n">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U72" t="n">
+      <c r="V72" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7042,7 +7386,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -7072,13 +7416,18 @@
           <t>ACGT</t>
         </is>
       </c>
-      <c r="T73" t="n">
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U73" t="n">
+      <c r="V73" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7134,7 +7483,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -7164,13 +7513,18 @@
           <t>AAGGTGTTAGATTGATCACGTT</t>
         </is>
       </c>
-      <c r="T74" t="n">
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U74" t="n">
+      <c r="V74" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7226,7 +7580,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -7256,13 +7610,18 @@
           <t>AAGGTGTTAGATTGATCACGTTT</t>
         </is>
       </c>
-      <c r="T75" t="n">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U75" t="n">
+      <c r="V75" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7318,7 +7677,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -7348,13 +7707,18 @@
           <t>GATTGATCACGTTTC</t>
         </is>
       </c>
-      <c r="T76" t="n">
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U76" t="n">
+      <c r="V76" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7410,7 +7774,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -7440,13 +7804,18 @@
           <t>GATCACGTTTC</t>
         </is>
       </c>
-      <c r="T77" t="n">
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U77" t="n">
+      <c r="V77" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7502,7 +7871,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -7532,13 +7901,18 @@
           <t>GGCAAGGTGTTAGATTGATCACGTTTCC</t>
         </is>
       </c>
-      <c r="T78" t="n">
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7594,7 +7968,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -7624,13 +7998,18 @@
           <t>GGTGTTAGATTGATCACGTTTCC</t>
         </is>
       </c>
-      <c r="T79" t="n">
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7686,7 +8065,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -7716,13 +8095,18 @@
           <t>TGTTAGATTGATCACGTTTCCA</t>
         </is>
       </c>
-      <c r="T80" t="n">
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U80" t="n">
+      <c r="V80" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7778,7 +8162,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -7808,13 +8192,18 @@
           <t>TGATCACGTTTCCA</t>
         </is>
       </c>
-      <c r="T81" t="n">
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U81" t="n">
+      <c r="V81" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7870,7 +8259,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -7900,13 +8289,18 @@
           <t>GCAAGGTGTTAGATTGATCACGTTTCCAGC</t>
         </is>
       </c>
-      <c r="T82" t="n">
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U82" t="n">
+      <c r="V82" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -7962,7 +8356,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
@@ -7992,13 +8386,18 @@
           <t>TGTTAGATTGATCACGTTTCCAGCA</t>
         </is>
       </c>
-      <c r="T83" t="n">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U83" t="n">
+      <c r="V83" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -8054,7 +8453,7 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
@@ -8084,13 +8483,18 @@
           <t>TGATCACGTTTCCAGCA</t>
         </is>
       </c>
-      <c r="T84" t="n">
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U84" t="n">
+      <c r="V84" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -8146,7 +8550,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -8176,13 +8580,18 @@
           <t>GCGC</t>
         </is>
       </c>
-      <c r="T85" t="n">
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U85" t="n">
+      <c r="V85" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8238,7 +8647,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -8268,13 +8677,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="T86" t="n">
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U86" t="n">
+      <c r="V86" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="W86" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8330,7 +8744,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -8360,13 +8774,18 @@
           <t>CAAATCA</t>
         </is>
       </c>
-      <c r="T87" t="n">
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U87" t="n">
+      <c r="V87" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="W87" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8422,7 +8841,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
@@ -8452,13 +8871,18 @@
           <t>CAAATCACA</t>
         </is>
       </c>
-      <c r="T88" t="n">
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U88" t="n">
+      <c r="V88" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8514,7 +8938,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
@@ -8544,13 +8968,18 @@
           <t>CACA</t>
         </is>
       </c>
-      <c r="T89" t="n">
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U89" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U89" t="n">
+      <c r="V89" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8606,7 +9035,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0.3311</v>
+        <v>0.3343</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -8636,13 +9065,18 @@
           <t>AGTGCGCCAAATCACAG</t>
         </is>
       </c>
-      <c r="T90" t="n">
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U90" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U90" t="n">
+      <c r="V90" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="W90" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -8698,7 +9132,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -8728,13 +9162,18 @@
           <t>GTGCGCCAAATCAC</t>
         </is>
       </c>
-      <c r="T91" t="n">
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U91" t="n">
         <v>0.5715713714514195</v>
       </c>
-      <c r="U91" t="n">
+      <c r="V91" t="n">
         <v>0.4284286285485805</v>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="W91" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -8790,7 +9229,7 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -8820,13 +9259,18 @@
           <t>GCGC</t>
         </is>
       </c>
-      <c r="T92" t="n">
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U92" t="n">
+      <c r="V92" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="W92" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -8882,7 +9326,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
@@ -8912,13 +9356,18 @@
           <t>TGCGCCA</t>
         </is>
       </c>
-      <c r="T93" t="n">
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U93" t="n">
+      <c r="V93" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="W93" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -8974,7 +9423,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -9004,13 +9453,18 @@
           <t>TGCGCCAAATCACA</t>
         </is>
       </c>
-      <c r="T94" t="n">
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U94" t="n">
+      <c r="V94" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V94" t="inlineStr">
+      <c r="W94" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -9066,7 +9520,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -9096,13 +9550,18 @@
           <t>TCACAGA</t>
         </is>
       </c>
-      <c r="T95" t="n">
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U95" t="n">
+      <c r="V95" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="W95" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -9158,7 +9617,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.2406</v>
+        <v>0.2811</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
@@ -9188,13 +9647,18 @@
           <t>ATCAATC</t>
         </is>
       </c>
-      <c r="T96" t="n">
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U96" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="U96" t="n">
+      <c r="V96" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="V96" t="inlineStr">
+      <c r="W96" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -9250,7 +9714,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>0.2406</v>
+        <v>0.2811</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
@@ -9280,13 +9744,18 @@
           <t>TCAATCTCA</t>
         </is>
       </c>
-      <c r="T97" t="n">
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U97" t="n">
         <v>0.5983606557377049</v>
       </c>
-      <c r="U97" t="n">
+      <c r="V97" t="n">
         <v>0.4016393442622951</v>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -9342,7 +9811,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0.2406</v>
+        <v>0.2811</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
@@ -9372,13 +9841,18 @@
           <t>TCTC</t>
         </is>
       </c>
-      <c r="T98" t="n">
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U98" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U98" t="n">
+      <c r="V98" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="W98" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -9434,7 +9908,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0.3008</v>
+        <v>0.2454</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -9464,13 +9938,18 @@
           <t>TTATCAA</t>
         </is>
       </c>
-      <c r="T99" t="n">
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U99" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -9526,7 +10005,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0.3008</v>
+        <v>0.2454</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
@@ -9556,13 +10035,18 @@
           <t>ATCAAT</t>
         </is>
       </c>
-      <c r="T100" t="n">
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U100" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="W100" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -9618,7 +10102,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>0.3008</v>
+        <v>0.2454</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
@@ -9648,13 +10132,18 @@
           <t>AGCGTTATCAATCT</t>
         </is>
       </c>
-      <c r="T101" t="n">
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U101" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U101" t="n">
+      <c r="V101" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V101" t="inlineStr">
+      <c r="W101" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -9706,7 +10195,7 @@
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
-        <v>0.0885</v>
+        <v>0.1365</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
@@ -9720,15 +10209,16 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
-      <c r="T102" t="n">
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="n">
         <v>1</v>
       </c>
-      <c r="U102" t="n">
+      <c r="V102" t="n">
         <v>0</v>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -9778,7 +10268,7 @@
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0925</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
@@ -9792,15 +10282,16 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
-      <c r="T103" t="n">
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="n">
         <v>1</v>
       </c>
-      <c r="U103" t="n">
+      <c r="V103" t="n">
         <v>0</v>
       </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -9850,7 +10341,7 @@
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>0.0579</v>
+        <v>0.1148</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
@@ -9864,15 +10355,16 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="n">
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="n">
         <v>1</v>
       </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>0</v>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -9922,7 +10414,7 @@
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
-        <v>0.1119</v>
+        <v>0.0638</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
@@ -9936,15 +10428,16 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
-      <c r="T105" t="n">
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="n">
         <v>1</v>
       </c>
-      <c r="U105" t="n">
+      <c r="V105" t="n">
         <v>0</v>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10487,7 @@
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>0.0838</v>
+        <v>0.0799</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
@@ -10008,15 +10501,16 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="n">
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="n">
         <v>1</v>
       </c>
-      <c r="U106" t="n">
+      <c r="V106" t="n">
         <v>0</v>
       </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10564,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>0.3028</v>
+        <v>0.3093</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
@@ -10100,13 +10594,18 @@
           <t>GACATAGATC</t>
         </is>
       </c>
-      <c r="T107" t="n">
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U107" t="n">
         <v>0.02998800479808077</v>
       </c>
-      <c r="U107" t="n">
+      <c r="V107" t="n">
         <v>0.9700119952019193</v>
       </c>
-      <c r="V107" t="inlineStr">
+      <c r="W107" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -10158,7 +10657,7 @@
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
@@ -10172,15 +10671,16 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
-      <c r="T108" t="n">
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="n">
         <v>1</v>
       </c>
-      <c r="U108" t="n">
+      <c r="V108" t="n">
         <v>0</v>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10730,7 @@
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>0.1152</v>
+        <v>0.1158</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
@@ -10244,15 +10744,16 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
-      <c r="T109" t="n">
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="n">
         <v>1</v>
       </c>
-      <c r="U109" t="n">
+      <c r="V109" t="n">
         <v>0</v>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10807,7 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>0.2227</v>
+        <v>0.2515</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -10340,13 +10841,18 @@
           <t>ATAAAAAT</t>
         </is>
       </c>
-      <c r="T110" t="n">
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U110" t="n">
         <v>0.6895241903238705</v>
       </c>
-      <c r="U110" t="n">
+      <c r="V110" t="n">
         <v>0.3104758096761295</v>
       </c>
-      <c r="V110" t="inlineStr">
+      <c r="W110" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -10402,7 +10908,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0.2319</v>
+        <v>0.2298</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -10436,13 +10942,18 @@
           <t>ACCTAATAAAAATAAGGT</t>
         </is>
       </c>
-      <c r="T111" t="n">
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U111" t="n">
         <v>0.009196321471411436</v>
       </c>
-      <c r="U111" t="n">
+      <c r="V111" t="n">
         <v>0.9908036785285885</v>
       </c>
-      <c r="V111" t="inlineStr">
+      <c r="W111" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -10498,7 +11009,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>0.2319</v>
+        <v>0.2298</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -10532,13 +11043,18 @@
           <t>ATAAAAAT</t>
         </is>
       </c>
-      <c r="T112" t="n">
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U112" t="n">
         <v>0.8778488604558177</v>
       </c>
-      <c r="U112" t="n">
+      <c r="V112" t="n">
         <v>0.1221511395441823</v>
       </c>
-      <c r="V112" t="inlineStr">
+      <c r="W112" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -10594,7 +11110,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0.1684</v>
+        <v>0.2204</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -10628,13 +11144,18 @@
           <t>ACACA</t>
         </is>
       </c>
-      <c r="T113" t="n">
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U113" t="n">
         <v>0.2872850859656138</v>
       </c>
-      <c r="U113" t="n">
+      <c r="V113" t="n">
         <v>0.7127149140343862</v>
       </c>
-      <c r="V113" t="inlineStr">
+      <c r="W113" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -10690,7 +11211,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0.1684</v>
+        <v>0.2204</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -10724,13 +11245,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T114" t="n">
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U114" t="n">
         <v>0.9668132746901239</v>
       </c>
-      <c r="U114" t="n">
+      <c r="V114" t="n">
         <v>0.0331867253098761</v>
       </c>
-      <c r="V114" t="inlineStr">
+      <c r="W114" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -10786,7 +11312,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0.1857</v>
+        <v>0.1893</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -10820,13 +11346,18 @@
           <t>AACACATGTT</t>
         </is>
       </c>
-      <c r="T115" t="n">
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U115" t="n">
         <v>0.1273490603758497</v>
       </c>
-      <c r="U115" t="n">
+      <c r="V115" t="n">
         <v>0.8726509396241503</v>
       </c>
-      <c r="V115" t="inlineStr">
+      <c r="W115" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -10882,7 +11413,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0.1857</v>
+        <v>0.1893</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -10916,13 +11447,18 @@
           <t>ACATGT</t>
         </is>
       </c>
-      <c r="T116" t="n">
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U116" t="n">
         <v>0.541983206717313</v>
       </c>
-      <c r="U116" t="n">
+      <c r="V116" t="n">
         <v>0.458016793282687</v>
       </c>
-      <c r="V116" t="inlineStr">
+      <c r="W116" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -10978,7 +11514,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>0.1857</v>
+        <v>0.1893</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -11012,13 +11548,18 @@
           <t>AACACATGTTT</t>
         </is>
       </c>
-      <c r="T117" t="n">
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U117" t="n">
         <v>0.9970011995201919</v>
       </c>
-      <c r="U117" t="n">
+      <c r="V117" t="n">
         <v>0.00299880047980805</v>
       </c>
-      <c r="V117" t="inlineStr">
+      <c r="W117" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -11074,7 +11615,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.1689</v>
+        <v>0.173</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -11108,13 +11649,18 @@
           <t>GTGT</t>
         </is>
       </c>
-      <c r="T118" t="n">
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U118" t="n">
         <v>0.937624950019992</v>
       </c>
-      <c r="U118" t="n">
+      <c r="V118" t="n">
         <v>0.06237504998000798</v>
       </c>
-      <c r="V118" t="inlineStr">
+      <c r="W118" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -11170,7 +11716,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>0.1729</v>
+        <v>0.224</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -11204,13 +11750,18 @@
           <t>GAACAGGTGTTC</t>
         </is>
       </c>
-      <c r="T119" t="n">
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U119" t="n">
         <v>0.00699720111955218</v>
       </c>
-      <c r="U119" t="n">
+      <c r="V119" t="n">
         <v>0.9930027988804478</v>
       </c>
-      <c r="V119" t="inlineStr">
+      <c r="W119" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -11266,7 +11817,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>0.1729</v>
+        <v>0.224</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -11300,13 +11851,18 @@
           <t>ACAGGT</t>
         </is>
       </c>
-      <c r="T120" t="n">
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U120" t="n">
         <v>0.975609756097561</v>
       </c>
-      <c r="U120" t="n">
+      <c r="V120" t="n">
         <v>0.02439024390243905</v>
       </c>
-      <c r="V120" t="inlineStr">
+      <c r="W120" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -11362,7 +11918,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.227</v>
+        <v>0.2382</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -11396,13 +11952,18 @@
           <t>TCGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T121" t="n">
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U121" t="n">
         <v>0.6067572970811675</v>
       </c>
-      <c r="U121" t="n">
+      <c r="V121" t="n">
         <v>0.3932427029188325</v>
       </c>
-      <c r="V121" t="inlineStr">
+      <c r="W121" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -11458,7 +12019,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0.227</v>
+        <v>0.2382</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -11492,13 +12053,18 @@
           <t>GTGT</t>
         </is>
       </c>
-      <c r="T122" t="n">
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U122" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U122" t="n">
+      <c r="V122" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V122" t="inlineStr">
+      <c r="W122" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -11554,7 +12120,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0.227</v>
+        <v>0.2382</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -11588,13 +12154,18 @@
           <t>GGTGTTCGG</t>
         </is>
       </c>
-      <c r="T123" t="n">
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U123" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U123" t="n">
+      <c r="V123" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V123" t="inlineStr">
+      <c r="W123" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -11650,7 +12221,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0.2784</v>
+        <v>0.2722</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -11684,13 +12255,18 @@
           <t>CGAACAGGTGTTCG</t>
         </is>
       </c>
-      <c r="T124" t="n">
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U124" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U124" t="n">
+      <c r="V124" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V124" t="inlineStr">
+      <c r="W124" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -11746,7 +12322,7 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>0.2784</v>
+        <v>0.2722</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -11780,13 +12356,18 @@
           <t>TCGA</t>
         </is>
       </c>
-      <c r="T125" t="n">
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U125" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="U125" t="n">
+      <c r="V125" t="n">
         <v>0.001799280287884897</v>
       </c>
-      <c r="V125" t="inlineStr">
+      <c r="W125" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -11842,7 +12423,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>0.2784</v>
+        <v>0.2722</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -11876,13 +12457,18 @@
           <t>ACAGGT</t>
         </is>
       </c>
-      <c r="T126" t="n">
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U126" t="n">
         <v>0.9982007197121151</v>
       </c>
-      <c r="U126" t="n">
+      <c r="V126" t="n">
         <v>0.001799280287884897</v>
       </c>
-      <c r="V126" t="inlineStr">
+      <c r="W126" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -11938,7 +12524,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>0.1983</v>
+        <v>0.1986</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -11972,13 +12558,18 @@
           <t>GAACAACACAGGAAC</t>
         </is>
       </c>
-      <c r="T127" t="n">
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U127" t="n">
         <v>0.02199120351859256</v>
       </c>
-      <c r="U127" t="n">
+      <c r="V127" t="n">
         <v>0.9780087964814075</v>
       </c>
-      <c r="V127" t="inlineStr">
+      <c r="W127" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -12030,7 +12621,7 @@
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
-        <v>0.0588</v>
+        <v>0.0605</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -12048,15 +12639,16 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
-      <c r="T128" t="n">
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="n">
         <v>1</v>
       </c>
-      <c r="U128" t="n">
+      <c r="V128" t="n">
         <v>0</v>
       </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12702,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>0.2683</v>
+        <v>0.2721</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -12144,13 +12736,18 @@
           <t>GAAGAAAAGGCGA</t>
         </is>
       </c>
-      <c r="T129" t="n">
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U129" t="n">
         <v>0.3024790083966413</v>
       </c>
-      <c r="U129" t="n">
+      <c r="V129" t="n">
         <v>0.6975209916033587</v>
       </c>
-      <c r="V129" t="inlineStr">
+      <c r="W129" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -12202,7 +12799,7 @@
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
-        <v>0.0694</v>
+        <v>0.0696</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -12220,15 +12817,16 @@
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
-      <c r="T130" t="n">
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="n">
         <v>1</v>
       </c>
-      <c r="U130" t="n">
+      <c r="V130" t="n">
         <v>0</v>
       </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12880,7 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>0.2919</v>
+        <v>0.2699</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -12316,13 +12914,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T131" t="n">
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U131" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U131" t="n">
+      <c r="V131" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V131" t="inlineStr">
+      <c r="W131" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -12374,7 +12977,7 @@
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
-        <v>0.0752</v>
+        <v>0.081</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -12392,15 +12995,16 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
-      <c r="T132" t="n">
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="n">
         <v>1</v>
       </c>
-      <c r="U132" t="n">
+      <c r="V132" t="n">
         <v>0</v>
       </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -12454,7 +13058,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>0.2327</v>
+        <v>0.1927</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
@@ -12484,13 +13088,18 @@
           <t>GAACAAGACCGGAAC</t>
         </is>
       </c>
-      <c r="T133" t="n">
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U133" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U133" t="n">
+      <c r="V133" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V133" t="inlineStr">
+      <c r="W133" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -12542,7 +13151,7 @@
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
-        <v>0.0624</v>
+        <v>0.1314</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
@@ -12556,15 +13165,16 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
-      <c r="T134" t="n">
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="n">
         <v>1</v>
       </c>
-      <c r="U134" t="n">
+      <c r="V134" t="n">
         <v>0</v>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -12618,7 +13228,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>0.2582</v>
+        <v>0.2525</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
@@ -12648,13 +13258,18 @@
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T135" t="n">
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U135" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U135" t="n">
+      <c r="V135" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V135" t="inlineStr">
+      <c r="W135" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -12710,7 +13325,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>0.2893</v>
+        <v>0.3006</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
@@ -12740,13 +13355,18 @@
           <t>TCGAACACATGTTCGA</t>
         </is>
       </c>
-      <c r="T136" t="n">
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U136" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U136" t="n">
+      <c r="V136" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V136" t="inlineStr">
+      <c r="W136" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -12802,7 +13422,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>0.2893</v>
+        <v>0.3006</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
@@ -12832,13 +13452,18 @@
           <t>TCGA</t>
         </is>
       </c>
-      <c r="T137" t="n">
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U137" t="n">
         <v>0.469812075169932</v>
       </c>
-      <c r="U137" t="n">
+      <c r="V137" t="n">
         <v>0.530187924830068</v>
       </c>
-      <c r="V137" t="inlineStr">
+      <c r="W137" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -12890,7 +13515,7 @@
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
-        <v>0.0788</v>
+        <v>0.0877</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
@@ -12904,15 +13529,16 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
-      <c r="T138" t="n">
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="n">
         <v>1</v>
       </c>
-      <c r="U138" t="n">
+      <c r="V138" t="n">
         <v>0</v>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -12966,7 +13592,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>0.2567</v>
+        <v>0.31</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
@@ -12996,13 +13622,18 @@
           <t>CTGGATATATATACAG</t>
         </is>
       </c>
-      <c r="T139" t="n">
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U139" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U139" t="n">
+      <c r="V139" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V139" t="inlineStr">
+      <c r="W139" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -13058,7 +13689,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -13092,13 +13723,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T140" t="n">
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U140" t="n">
         <v>0.03978408636545382</v>
       </c>
-      <c r="U140" t="n">
+      <c r="V140" t="n">
         <v>0.9602159136345462</v>
       </c>
-      <c r="V140" t="inlineStr">
+      <c r="W140" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -13154,7 +13790,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -13188,13 +13824,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T141" t="n">
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U141" t="n">
         <v>0.1689324270291883</v>
       </c>
-      <c r="U141" t="n">
+      <c r="V141" t="n">
         <v>0.8310675729708117</v>
       </c>
-      <c r="V141" t="inlineStr">
+      <c r="W141" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13250,7 +13891,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -13284,13 +13925,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T142" t="n">
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U142" t="n">
         <v>0.5373850459816074</v>
       </c>
-      <c r="U142" t="n">
+      <c r="V142" t="n">
         <v>0.4626149540183926</v>
       </c>
-      <c r="V142" t="inlineStr">
+      <c r="W142" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13346,7 +13992,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -13380,13 +14026,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T143" t="n">
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U143" t="n">
         <v>0.9854058376649341</v>
       </c>
-      <c r="U143" t="n">
+      <c r="V143" t="n">
         <v>0.01459416233506594</v>
       </c>
-      <c r="V143" t="inlineStr">
+      <c r="W143" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13442,7 +14093,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -13476,13 +14127,18 @@
           <t>TGTTTTTTTGT</t>
         </is>
       </c>
-      <c r="T144" t="n">
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U144" t="n">
         <v>0.9854058376649341</v>
       </c>
-      <c r="U144" t="n">
+      <c r="V144" t="n">
         <v>0.01459416233506594</v>
       </c>
-      <c r="V144" t="inlineStr">
+      <c r="W144" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13538,7 +14194,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -13572,13 +14228,18 @@
           <t>TTTTTTT</t>
         </is>
       </c>
-      <c r="T145" t="n">
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U145" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U145" t="n">
+      <c r="V145" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V145" t="inlineStr">
+      <c r="W145" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13634,7 +14295,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -13668,13 +14329,18 @@
           <t>ACTGTTTTTTTGTAC</t>
         </is>
       </c>
-      <c r="T146" t="n">
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U146" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U146" t="n">
+      <c r="V146" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V146" t="inlineStr">
+      <c r="W146" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13730,7 +14396,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -13764,13 +14430,18 @@
           <t>GTTTTTTTGTACAGT</t>
         </is>
       </c>
-      <c r="T147" t="n">
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U147" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U147" t="n">
+      <c r="V147" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V147" t="inlineStr">
+      <c r="W147" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13826,7 +14497,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>0.3854</v>
+        <v>0.3524</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -13860,13 +14531,18 @@
           <t>GTACAGT</t>
         </is>
       </c>
-      <c r="T148" t="n">
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U148" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U148" t="n">
+      <c r="V148" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V148" t="inlineStr">
+      <c r="W148" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -13922,7 +14598,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -13956,13 +14632,18 @@
           <t>GACTGTTTTTTTGTACAGTC</t>
         </is>
       </c>
-      <c r="T149" t="n">
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U149" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U149" t="n">
+      <c r="V149" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V149" t="inlineStr">
+      <c r="W149" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -14018,7 +14699,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -14052,13 +14733,18 @@
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="T150" t="n">
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U150" t="n">
         <v>0.616953218712515</v>
       </c>
-      <c r="U150" t="n">
+      <c r="V150" t="n">
         <v>0.383046781287485</v>
       </c>
-      <c r="V150" t="inlineStr">
+      <c r="W150" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -14114,7 +14800,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -14148,13 +14834,18 @@
           <t>ACTGT</t>
         </is>
       </c>
-      <c r="T151" t="n">
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U151" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U151" t="n">
+      <c r="V151" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V151" t="inlineStr">
+      <c r="W151" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -14210,7 +14901,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -14244,13 +14935,18 @@
           <t>ACTGTTTTTTTGT</t>
         </is>
       </c>
-      <c r="T152" t="n">
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U152" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U152" t="n">
+      <c r="V152" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V152" t="inlineStr">
+      <c r="W152" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -14306,7 +15002,7 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>0.2901</v>
+        <v>0.3451</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -14340,13 +15036,18 @@
           <t>ACAGT</t>
         </is>
       </c>
-      <c r="T153" t="n">
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U153" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U153" t="n">
+      <c r="V153" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V153" t="inlineStr">
+      <c r="W153" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -14398,7 +15099,7 @@
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
-        <v>0.1345</v>
+        <v>0.079</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -14416,15 +15117,16 @@
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="n">
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="n">
         <v>1</v>
       </c>
-      <c r="U154" t="n">
+      <c r="V154" t="n">
         <v>0</v>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -14478,7 +15180,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>0.2381</v>
+        <v>0.2885</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -14512,13 +15214,18 @@
           <t>CTGTATTTATATACAG</t>
         </is>
       </c>
-      <c r="T155" t="n">
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U155" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U155" t="n">
+      <c r="V155" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V155" t="inlineStr">
+      <c r="W155" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -14574,7 +15281,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>0.2469</v>
+        <v>0.1962</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -14608,13 +15315,18 @@
           <t>CAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T156" t="n">
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U156" t="n">
         <v>0.1239504198320672</v>
       </c>
-      <c r="U156" t="n">
+      <c r="V156" t="n">
         <v>0.8760495801679329</v>
       </c>
-      <c r="V156" t="inlineStr">
+      <c r="W156" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -14670,7 +15382,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>0.1942</v>
+        <v>0.1917</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -14704,13 +15416,18 @@
           <t>TGCTCAAAGGGGCA</t>
         </is>
       </c>
-      <c r="T157" t="n">
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U157" t="n">
         <v>0.1603358656537385</v>
       </c>
-      <c r="U157" t="n">
+      <c r="V157" t="n">
         <v>0.8396641343462615</v>
       </c>
-      <c r="V157" t="inlineStr">
+      <c r="W157" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -14762,7 +15479,7 @@
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
-        <v>0.06</v>
+        <v>0.1079</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -14780,15 +15497,16 @@
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="inlineStr"/>
-      <c r="T158" t="n">
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="n">
         <v>1</v>
       </c>
-      <c r="U158" t="n">
+      <c r="V158" t="n">
         <v>0</v>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -14842,7 +15560,7 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>0.2258</v>
+        <v>0.179</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -14876,13 +15594,18 @@
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T159" t="n">
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U159" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U159" t="n">
+      <c r="V159" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V159" t="inlineStr">
+      <c r="W159" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -14938,7 +15661,7 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>0.1961</v>
+        <v>0.1999</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -14972,13 +15695,18 @@
           <t>AACAA</t>
         </is>
       </c>
-      <c r="T160" t="n">
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U160" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U160" t="n">
+      <c r="V160" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V160" t="inlineStr">
+      <c r="W160" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -15034,7 +15762,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>0.1961</v>
+        <v>0.1999</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -15068,13 +15796,18 @@
           <t>AGAACAAG</t>
         </is>
       </c>
-      <c r="T161" t="n">
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U161" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U161" t="n">
+      <c r="V161" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V161" t="inlineStr">
+      <c r="W161" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -15130,7 +15863,7 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>0.1961</v>
+        <v>0.1999</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -15164,13 +15897,18 @@
           <t>GTGT</t>
         </is>
       </c>
-      <c r="T162" t="n">
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U162" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="U162" t="n">
+      <c r="V162" t="n">
         <v>0.001199520191923265</v>
       </c>
-      <c r="V162" t="inlineStr">
+      <c r="W162" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -15226,7 +15964,7 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>0.214</v>
+        <v>0.259</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -15260,13 +15998,18 @@
           <t>AGAACAAGTGTTCT</t>
         </is>
       </c>
-      <c r="T163" t="n">
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U163" t="n">
         <v>0.005997600959616154</v>
       </c>
-      <c r="U163" t="n">
+      <c r="V163" t="n">
         <v>0.9940023990403839</v>
       </c>
-      <c r="V163" t="inlineStr">
+      <c r="W163" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -15322,7 +16065,7 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>0.214</v>
+        <v>0.259</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -15356,13 +16099,18 @@
           <t>ACAAGT</t>
         </is>
       </c>
-      <c r="T164" t="n">
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U164" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U164" t="n">
+      <c r="V164" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V164" t="inlineStr">
+      <c r="W164" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -15418,7 +16166,7 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>0.214</v>
+        <v>0.259</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -15452,13 +16200,18 @@
           <t>AAGTGTT</t>
         </is>
       </c>
-      <c r="T165" t="n">
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U165" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U165" t="n">
+      <c r="V165" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V165" t="inlineStr">
+      <c r="W165" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -15514,7 +16267,7 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>0.214</v>
+        <v>0.259</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -15548,13 +16301,18 @@
           <t>AGTGTTCT</t>
         </is>
       </c>
-      <c r="T166" t="n">
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U166" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U166" t="n">
+      <c r="V166" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V166" t="inlineStr">
+      <c r="W166" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -15606,7 +16364,7 @@
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
-        <v>0.1177</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
@@ -15620,15 +16378,16 @@
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
-      <c r="T167" t="n">
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="n">
         <v>1</v>
       </c>
-      <c r="U167" t="n">
+      <c r="V167" t="n">
         <v>0</v>
       </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -15682,7 +16441,7 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>0.2389</v>
+        <v>0.2982</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
@@ -15712,13 +16471,18 @@
           <t>CTGTATAAATATACAG</t>
         </is>
       </c>
-      <c r="T168" t="n">
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U168" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U168" t="n">
+      <c r="V168" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V168" t="inlineStr">
+      <c r="W168" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -15770,7 +16534,7 @@
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
-        <v>0.1048</v>
+        <v>0.0644</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
@@ -15784,15 +16548,16 @@
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
-      <c r="T169" t="n">
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="n">
         <v>1</v>
       </c>
-      <c r="U169" t="n">
+      <c r="V169" t="n">
         <v>0</v>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -15846,7 +16611,7 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>0.1946</v>
+        <v>0.1965</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
@@ -15876,13 +16641,18 @@
           <t>CTGTACATCAATACAG</t>
         </is>
       </c>
-      <c r="T170" t="n">
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U170" t="n">
         <v>0.001399440223910436</v>
       </c>
-      <c r="U170" t="n">
+      <c r="V170" t="n">
         <v>0.9986005597760895</v>
       </c>
-      <c r="V170" t="inlineStr">
+      <c r="W170" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -15938,7 +16708,7 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>0.2693</v>
+        <v>0.274</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -15972,13 +16742,18 @@
           <t>TGACACATG</t>
         </is>
       </c>
-      <c r="T171" t="n">
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U171" t="n">
         <v>0.8866453418632547</v>
       </c>
-      <c r="U171" t="n">
+      <c r="V171" t="n">
         <v>0.1133546581367453</v>
       </c>
-      <c r="V171" t="inlineStr">
+      <c r="W171" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -16034,7 +16809,7 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>0.2693</v>
+        <v>0.274</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -16068,13 +16843,18 @@
           <t>GTTGACACATGT</t>
         </is>
       </c>
-      <c r="T172" t="n">
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U172" t="n">
         <v>0.8866453418632547</v>
       </c>
-      <c r="U172" t="n">
+      <c r="V172" t="n">
         <v>0.1133546581367453</v>
       </c>
-      <c r="V172" t="inlineStr">
+      <c r="W172" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -16130,7 +16910,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>0.2334</v>
+        <v>0.2458</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -16164,13 +16944,18 @@
           <t>GGTTGACACATGTAAACC</t>
         </is>
       </c>
-      <c r="T173" t="n">
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U173" t="n">
         <v>0.2387045181927229</v>
       </c>
-      <c r="U173" t="n">
+      <c r="V173" t="n">
         <v>0.7612954818072771</v>
       </c>
-      <c r="V173" t="inlineStr">
+      <c r="W173" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -16226,7 +17011,7 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>0.2334</v>
+        <v>0.2458</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -16260,13 +17045,18 @@
           <t>TGACA</t>
         </is>
       </c>
-      <c r="T174" t="n">
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U174" t="n">
         <v>0.9594162335065973</v>
       </c>
-      <c r="U174" t="n">
+      <c r="V174" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="V174" t="inlineStr">
+      <c r="W174" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -16322,7 +17112,7 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>0.2334</v>
+        <v>0.2458</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -16356,13 +17146,18 @@
           <t>CACATG</t>
         </is>
       </c>
-      <c r="T175" t="n">
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U175" t="n">
         <v>0.9594162335065973</v>
       </c>
-      <c r="U175" t="n">
+      <c r="V175" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="V175" t="inlineStr">
+      <c r="W175" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -16418,7 +17213,7 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>0.2334</v>
+        <v>0.2458</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -16452,13 +17247,18 @@
           <t>GTAAAC</t>
         </is>
       </c>
-      <c r="T176" t="n">
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U176" t="n">
         <v>0.9594162335065973</v>
       </c>
-      <c r="U176" t="n">
+      <c r="V176" t="n">
         <v>0.04058376649340267</v>
       </c>
-      <c r="V176" t="inlineStr">
+      <c r="W176" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -16514,7 +17314,7 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>0.1657</v>
+        <v>0.2157</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
@@ -16544,13 +17344,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T177" t="n">
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U177" t="n">
         <v>0.2477009196321471</v>
       </c>
-      <c r="U177" t="n">
+      <c r="V177" t="n">
         <v>0.7522990803678529</v>
       </c>
-      <c r="V177" t="inlineStr">
+      <c r="W177" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -16606,7 +17411,7 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>0.1657</v>
+        <v>0.2157</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
@@ -16636,13 +17441,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="T178" t="n">
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U178" t="n">
         <v>0.2477009196321471</v>
       </c>
-      <c r="U178" t="n">
+      <c r="V178" t="n">
         <v>0.7522990803678529</v>
       </c>
-      <c r="V178" t="inlineStr">
+      <c r="W178" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -16698,7 +17508,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>0.2098</v>
+        <v>0.1618</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
@@ -16728,13 +17538,18 @@
           <t>TTTGAAATTCAA</t>
         </is>
       </c>
-      <c r="T179" t="n">
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U179" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="U179" t="n">
+      <c r="V179" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="V179" t="inlineStr">
+      <c r="W179" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -16786,7 +17601,7 @@
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
@@ -16800,15 +17615,16 @@
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
-      <c r="T180" t="n">
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="n">
         <v>1</v>
       </c>
-      <c r="U180" t="n">
+      <c r="V180" t="n">
         <v>0</v>
       </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -16862,7 +17678,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>0.2663</v>
+        <v>0.2756</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
@@ -16892,13 +17708,18 @@
           <t>CTAAAAGCCCGTTCAG</t>
         </is>
       </c>
-      <c r="T181" t="n">
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U181" t="n">
         <v>0.8048780487804879</v>
       </c>
-      <c r="U181" t="n">
+      <c r="V181" t="n">
         <v>0.1951219512195121</v>
       </c>
-      <c r="V181" t="inlineStr">
+      <c r="W181" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -16950,7 +17771,7 @@
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="n">
-        <v>0.0625</v>
+        <v>0.0655</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
@@ -16964,15 +17785,16 @@
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
-      <c r="T182" t="n">
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="n">
         <v>1</v>
       </c>
-      <c r="U182" t="n">
+      <c r="V182" t="n">
         <v>0</v>
       </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17848,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>0.1873</v>
+        <v>0.2385</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
@@ -17056,13 +17878,18 @@
           <t>CTGTTTTTTTATACAG</t>
         </is>
       </c>
-      <c r="T183" t="n">
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U183" t="n">
         <v>0.002399040383846461</v>
       </c>
-      <c r="U183" t="n">
+      <c r="V183" t="n">
         <v>0.9976009596161536</v>
       </c>
-      <c r="V183" t="inlineStr">
+      <c r="W183" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -17114,7 +17941,7 @@
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="n">
-        <v>0.1068</v>
+        <v>0.0636</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -17132,15 +17959,16 @@
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
-      <c r="T184" t="n">
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="n">
         <v>1</v>
       </c>
-      <c r="U184" t="n">
+      <c r="V184" t="n">
         <v>0</v>
       </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -17194,7 +18022,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>0.1908</v>
+        <v>0.1948</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -17228,13 +18056,18 @@
           <t>AACAAATGTT</t>
         </is>
       </c>
-      <c r="T185" t="n">
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U185" t="n">
         <v>0.01819272291083567</v>
       </c>
-      <c r="U185" t="n">
+      <c r="V185" t="n">
         <v>0.9818072770891644</v>
       </c>
-      <c r="V185" t="inlineStr">
+      <c r="W185" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -17290,7 +18123,7 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>0.2018</v>
+        <v>0.2459</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
@@ -17320,13 +18153,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T186" t="n">
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U186" t="n">
         <v>0.9910035985605757</v>
       </c>
-      <c r="U186" t="n">
+      <c r="V186" t="n">
         <v>0.008996401439424262</v>
       </c>
-      <c r="V186" t="inlineStr">
+      <c r="W186" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -17382,7 +18220,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>0.2018</v>
+        <v>0.2459</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
@@ -17412,13 +18250,18 @@
           <t>TACACAGTA</t>
         </is>
       </c>
-      <c r="T187" t="n">
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U187" t="n">
         <v>0.9910035985605757</v>
       </c>
-      <c r="U187" t="n">
+      <c r="V187" t="n">
         <v>0.008996401439424262</v>
       </c>
-      <c r="V187" t="inlineStr">
+      <c r="W187" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -17474,7 +18317,7 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>0.2619</v>
+        <v>0.2121</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
@@ -17504,13 +18347,18 @@
           <t>TTACACAGTAA</t>
         </is>
       </c>
-      <c r="T188" t="n">
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U188" t="n">
         <v>0.05937624950019992</v>
       </c>
-      <c r="U188" t="n">
+      <c r="V188" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="V188" t="inlineStr">
+      <c r="W188" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -17566,7 +18414,7 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>0.2619</v>
+        <v>0.2121</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
@@ -17596,13 +18444,18 @@
           <t>TTTACACAGTAA</t>
         </is>
       </c>
-      <c r="T189" t="n">
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U189" t="n">
         <v>0.9964014394242303</v>
       </c>
-      <c r="U189" t="n">
+      <c r="V189" t="n">
         <v>0.003598560575769683</v>
       </c>
-      <c r="V189" t="inlineStr">
+      <c r="W189" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -17658,7 +18511,7 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>0.2604</v>
+        <v>0.3048</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
@@ -17688,13 +18541,18 @@
           <t>ATAAAT</t>
         </is>
       </c>
-      <c r="T190" t="n">
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U190" t="n">
         <v>0.4452219112355058</v>
       </c>
-      <c r="U190" t="n">
+      <c r="V190" t="n">
         <v>0.5547780887644942</v>
       </c>
-      <c r="V190" t="inlineStr">
+      <c r="W190" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -17750,7 +18608,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>0.3101</v>
+        <v>0.2657</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
@@ -17780,13 +18638,18 @@
           <t>CTGTATAAATAAACAG</t>
         </is>
       </c>
-      <c r="T191" t="n">
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U191" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U191" t="n">
+      <c r="V191" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V191" t="inlineStr">
+      <c r="W191" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -17842,7 +18705,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>0.1929</v>
+        <v>0.1948</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -17876,13 +18739,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T192" t="n">
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U192" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U192" t="n">
+      <c r="V192" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V192" t="inlineStr">
+      <c r="W192" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -17938,7 +18806,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>0.1929</v>
+        <v>0.1948</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -17972,13 +18840,18 @@
           <t>TATA</t>
         </is>
       </c>
-      <c r="T193" t="n">
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U193" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U193" t="n">
+      <c r="V193" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V193" t="inlineStr">
+      <c r="W193" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -18034,7 +18907,7 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>0.1929</v>
+        <v>0.1948</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -18068,13 +18941,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="T194" t="n">
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U194" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U194" t="n">
+      <c r="V194" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V194" t="inlineStr">
+      <c r="W194" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -18130,7 +19008,7 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>0.2573</v>
+        <v>0.2611</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -18164,13 +19042,18 @@
           <t>TTTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T195" t="n">
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U195" t="n">
         <v>0.2249100359856057</v>
       </c>
-      <c r="U195" t="n">
+      <c r="V195" t="n">
         <v>0.7750899640143942</v>
       </c>
-      <c r="V195" t="inlineStr">
+      <c r="W195" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18226,7 +19109,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>0.2573</v>
+        <v>0.2611</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -18260,13 +19143,18 @@
           <t>TATA</t>
         </is>
       </c>
-      <c r="T196" t="n">
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U196" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U196" t="n">
+      <c r="V196" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V196" t="inlineStr">
+      <c r="W196" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18322,7 +19210,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>0.2573</v>
+        <v>0.2611</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -18356,13 +19244,18 @@
           <t>TTTGCTATACAA</t>
         </is>
       </c>
-      <c r="T197" t="n">
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U197" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U197" t="n">
+      <c r="V197" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V197" t="inlineStr">
+      <c r="W197" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18418,7 +19311,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>0.2573</v>
+        <v>0.2611</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -18452,13 +19345,18 @@
           <t>TTGCTATACAAA</t>
         </is>
       </c>
-      <c r="T198" t="n">
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U198" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U198" t="n">
+      <c r="V198" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V198" t="inlineStr">
+      <c r="W198" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18514,7 +19412,7 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>0.2036</v>
+        <v>0.2058</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -18548,13 +19446,18 @@
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T199" t="n">
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U199" t="n">
         <v>0.003798480607756897</v>
       </c>
-      <c r="U199" t="n">
+      <c r="V199" t="n">
         <v>0.9962015193922431</v>
       </c>
-      <c r="V199" t="inlineStr">
+      <c r="W199" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -18610,7 +19513,7 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>0.2036</v>
+        <v>0.2058</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -18644,13 +19547,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="T200" t="n">
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U200" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U200" t="n">
+      <c r="V200" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V200" t="inlineStr">
+      <c r="W200" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -18706,7 +19614,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>0.2134</v>
+        <v>0.2133</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -18740,13 +19648,18 @@
           <t>TGTACAAATGTACA</t>
         </is>
       </c>
-      <c r="T201" t="n">
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U201" t="n">
         <v>0.004798080767692923</v>
       </c>
-      <c r="U201" t="n">
+      <c r="V201" t="n">
         <v>0.9952019192323071</v>
       </c>
-      <c r="V201" t="inlineStr">
+      <c r="W201" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -18802,7 +19715,7 @@
         </is>
       </c>
       <c r="K202" t="n">
-        <v>0.2134</v>
+        <v>0.2133</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -18836,13 +19749,18 @@
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="T202" t="n">
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U202" t="n">
         <v>0.6867253098760496</v>
       </c>
-      <c r="U202" t="n">
+      <c r="V202" t="n">
         <v>0.3132746901239504</v>
       </c>
-      <c r="V202" t="inlineStr">
+      <c r="W202" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18898,7 +19816,7 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>0.2134</v>
+        <v>0.2133</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -18932,13 +19850,18 @@
           <t>TGTACA</t>
         </is>
       </c>
-      <c r="T203" t="n">
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U203" t="n">
         <v>0.6867253098760496</v>
       </c>
-      <c r="U203" t="n">
+      <c r="V203" t="n">
         <v>0.3132746901239504</v>
       </c>
-      <c r="V203" t="inlineStr">
+      <c r="W203" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -18994,7 +19917,7 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -19028,13 +19951,18 @@
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T204" t="n">
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U204" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="U204" t="n">
+      <c r="V204" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="V204" t="inlineStr">
+      <c r="W204" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19090,7 +20018,7 @@
         </is>
       </c>
       <c r="K205" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -19124,13 +20052,18 @@
           <t>TGTTCTTGTTTTGTTC</t>
         </is>
       </c>
-      <c r="T205" t="n">
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U205" t="n">
         <v>0.6271491403438625</v>
       </c>
-      <c r="U205" t="n">
+      <c r="V205" t="n">
         <v>0.3728508596561375</v>
       </c>
-      <c r="V205" t="inlineStr">
+      <c r="W205" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19186,7 +20119,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -19220,13 +20153,18 @@
           <t>TGTTCTTGTT</t>
         </is>
       </c>
-      <c r="T206" t="n">
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U206" t="n">
         <v>0.9690123950419832</v>
       </c>
-      <c r="U206" t="n">
+      <c r="V206" t="n">
         <v>0.03098760495801678</v>
       </c>
-      <c r="V206" t="inlineStr">
+      <c r="W206" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19282,7 +20220,7 @@
         </is>
       </c>
       <c r="K207" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -19316,13 +20254,18 @@
           <t>TTTT</t>
         </is>
       </c>
-      <c r="T207" t="n">
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U207" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U207" t="n">
+      <c r="V207" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V207" t="inlineStr">
+      <c r="W207" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19378,7 +20321,7 @@
         </is>
       </c>
       <c r="K208" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -19412,13 +20355,18 @@
           <t>CTGTTCT</t>
         </is>
       </c>
-      <c r="T208" t="n">
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U208" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U208" t="n">
+      <c r="V208" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V208" t="inlineStr">
+      <c r="W208" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19474,7 +20422,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -19508,13 +20456,18 @@
           <t>TTCTT</t>
         </is>
       </c>
-      <c r="T209" t="n">
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U209" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U209" t="n">
+      <c r="V209" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V209" t="inlineStr">
+      <c r="W209" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19570,7 +20523,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -19604,13 +20557,18 @@
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="T210" t="n">
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U210" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U210" t="n">
+      <c r="V210" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V210" t="inlineStr">
+      <c r="W210" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19666,7 +20624,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -19700,13 +20658,18 @@
           <t>TTCTTGTTT</t>
         </is>
       </c>
-      <c r="T211" t="n">
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U211" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U211" t="n">
+      <c r="V211" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V211" t="inlineStr">
+      <c r="W211" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19762,7 +20725,7 @@
         </is>
       </c>
       <c r="K212" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -19796,13 +20759,18 @@
           <t>TTGTTT</t>
         </is>
       </c>
-      <c r="T212" t="n">
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U212" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U212" t="n">
+      <c r="V212" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V212" t="inlineStr">
+      <c r="W212" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19858,7 +20826,7 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -19892,13 +20860,18 @@
           <t>TTCTTGTTTT</t>
         </is>
       </c>
-      <c r="T213" t="n">
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U213" t="n">
+      <c r="V213" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V213" t="inlineStr">
+      <c r="W213" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -19954,7 +20927,7 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -19988,13 +20961,18 @@
           <t>TTTT</t>
         </is>
       </c>
-      <c r="T214" t="n">
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U214" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U214" t="n">
+      <c r="V214" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V214" t="inlineStr">
+      <c r="W214" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20050,7 +21028,7 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -20084,13 +21062,18 @@
           <t>TTGTTTTGTT</t>
         </is>
       </c>
-      <c r="T215" t="n">
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U215" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U215" t="n">
+      <c r="V215" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V215" t="inlineStr">
+      <c r="W215" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20146,7 +21129,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -20180,13 +21163,18 @@
           <t>TTTGTT</t>
         </is>
       </c>
-      <c r="T216" t="n">
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U216" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U216" t="n">
+      <c r="V216" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V216" t="inlineStr">
+      <c r="W216" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20242,7 +21230,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -20276,13 +21264,18 @@
           <t>TTGTT</t>
         </is>
       </c>
-      <c r="T217" t="n">
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U217" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U217" t="n">
+      <c r="V217" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V217" t="inlineStr">
+      <c r="W217" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20338,7 +21331,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -20372,13 +21365,18 @@
           <t>CTGTTCTTGTTTTGTTCCT</t>
         </is>
       </c>
-      <c r="T218" t="n">
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U218" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U218" t="n">
+      <c r="V218" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V218" t="inlineStr">
+      <c r="W218" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20434,7 +21432,7 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>0.5127</v>
+        <v>0.5129</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -20468,13 +21466,18 @@
           <t>CTTGTTTTGTTCCT</t>
         </is>
       </c>
-      <c r="T219" t="n">
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U219" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U219" t="n">
+      <c r="V219" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V219" t="inlineStr">
+      <c r="W219" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20526,7 +21529,7 @@
       </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="n">
-        <v>0.0717</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -20544,15 +21547,16 @@
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
-      <c r="T220" t="n">
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="n">
         <v>1</v>
       </c>
-      <c r="U220" t="n">
+      <c r="V220" t="n">
         <v>0</v>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -20602,7 +21606,7 @@
       </c>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="n">
-        <v>0.1479</v>
+        <v>0.1247</v>
       </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
@@ -20616,15 +21620,16 @@
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
-      <c r="T221" t="n">
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="n">
         <v>1</v>
       </c>
-      <c r="U221" t="n">
+      <c r="V221" t="n">
         <v>0</v>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -20678,7 +21683,7 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>0.2563</v>
+        <v>0.2547</v>
       </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
@@ -20708,13 +21713,18 @@
           <t>GAACATATGTTC</t>
         </is>
       </c>
-      <c r="T222" t="n">
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U222" t="n">
         <v>0.0003998400639744102</v>
       </c>
-      <c r="U222" t="n">
+      <c r="V222" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="V222" t="inlineStr">
+      <c r="W222" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -20770,7 +21780,7 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>0.2403</v>
+        <v>0.2453</v>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
@@ -20800,13 +21810,18 @@
           <t>GTACTTATGT</t>
         </is>
       </c>
-      <c r="T223" t="n">
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U223" t="n">
         <v>0.09956017592962815</v>
       </c>
-      <c r="U223" t="n">
+      <c r="V223" t="n">
         <v>0.9004398240703718</v>
       </c>
-      <c r="V223" t="inlineStr">
+      <c r="W223" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20862,7 +21877,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>0.2403</v>
+        <v>0.2453</v>
       </c>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
@@ -20892,13 +21907,18 @@
           <t>TACTTATGTACTA</t>
         </is>
       </c>
-      <c r="T224" t="n">
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U224" t="n">
         <v>0.5023990403838464</v>
       </c>
-      <c r="U224" t="n">
+      <c r="V224" t="n">
         <v>0.4976009596161536</v>
       </c>
-      <c r="V224" t="inlineStr">
+      <c r="W224" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -20950,7 +21970,7 @@
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="n">
-        <v>0.0639</v>
+        <v>0.0684</v>
       </c>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
@@ -20964,15 +21984,16 @@
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
-      <c r="T225" t="n">
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="n">
         <v>1</v>
       </c>
-      <c r="U225" t="n">
+      <c r="V225" t="n">
         <v>0</v>
       </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -21026,7 +22047,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>0.2351</v>
+        <v>0.2028</v>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
@@ -21056,13 +22077,18 @@
           <t>GTACTTATGT</t>
         </is>
       </c>
-      <c r="T226" t="n">
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U226" t="n">
         <v>0.09956017592962815</v>
       </c>
-      <c r="U226" t="n">
+      <c r="V226" t="n">
         <v>0.9004398240703718</v>
       </c>
-      <c r="V226" t="inlineStr">
+      <c r="W226" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -21118,7 +22144,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>0.2351</v>
+        <v>0.2028</v>
       </c>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
@@ -21148,13 +22174,18 @@
           <t>TACTTATGTACTA</t>
         </is>
       </c>
-      <c r="T227" t="n">
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U227" t="n">
         <v>0.5023990403838464</v>
       </c>
-      <c r="U227" t="n">
+      <c r="V227" t="n">
         <v>0.4976009596161536</v>
       </c>
-      <c r="V227" t="inlineStr">
+      <c r="W227" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -21206,7 +22237,7 @@
       </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="n">
-        <v>0.0641</v>
+        <v>0.1151</v>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
@@ -21220,15 +22251,16 @@
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
-      <c r="T228" t="n">
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="n">
         <v>1</v>
       </c>
-      <c r="U228" t="n">
+      <c r="V228" t="n">
         <v>0</v>
       </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -21282,7 +22314,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>0.23</v>
+        <v>0.2283</v>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
@@ -21312,13 +22344,18 @@
           <t>TCTTGATTTGTTC</t>
         </is>
       </c>
-      <c r="T229" t="n">
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U229" t="n">
         <v>0.4520191923230708</v>
       </c>
-      <c r="U229" t="n">
+      <c r="V229" t="n">
         <v>0.5479808076769292</v>
       </c>
-      <c r="V229" t="inlineStr">
+      <c r="W229" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -21370,7 +22407,7 @@
       </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="n">
-        <v>0.119</v>
+        <v>0.1173</v>
       </c>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
@@ -21384,15 +22421,16 @@
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
-      <c r="T230" t="n">
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="n">
         <v>1</v>
       </c>
-      <c r="U230" t="n">
+      <c r="V230" t="n">
         <v>0</v>
       </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -21446,7 +22484,7 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>0.2333</v>
+        <v>0.235</v>
       </c>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
@@ -21476,13 +22514,18 @@
           <t>TGTTCTCGTTATGTTC</t>
         </is>
       </c>
-      <c r="T231" t="n">
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U231" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U231" t="n">
+      <c r="V231" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V231" t="inlineStr">
+      <c r="W231" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -21534,7 +22577,7 @@
       </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="n">
-        <v>0.1155</v>
+        <v>0.1194</v>
       </c>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
@@ -21548,15 +22591,16 @@
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
-      <c r="T232" t="n">
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="n">
         <v>1</v>
       </c>
-      <c r="U232" t="n">
+      <c r="V232" t="n">
         <v>0</v>
       </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -21606,7 +22650,7 @@
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="n">
-        <v>0.0613</v>
+        <v>0.0611</v>
       </c>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
@@ -21620,15 +22664,16 @@
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
-      <c r="T233" t="n">
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="n">
         <v>1</v>
       </c>
-      <c r="U233" t="n">
+      <c r="V233" t="n">
         <v>0</v>
       </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -21682,7 +22727,7 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>0.1763</v>
+        <v>0.1775</v>
       </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
@@ -21712,13 +22757,18 @@
           <t>AACATATGTT</t>
         </is>
       </c>
-      <c r="T234" t="n">
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
         <v>0.04938024790083966</v>
       </c>
-      <c r="U234" t="n">
+      <c r="V234" t="n">
         <v>0.9506197520991604</v>
       </c>
-      <c r="V234" t="inlineStr">
+      <c r="W234" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -21774,7 +22824,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -21808,13 +22858,18 @@
           <t>TAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T235" t="n">
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U235" t="n">
         <v>0.726109556177529</v>
       </c>
-      <c r="U235" t="n">
+      <c r="V235" t="n">
         <v>0.273890443822471</v>
       </c>
-      <c r="V235" t="inlineStr">
+      <c r="W235" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -21870,7 +22925,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -21904,13 +22959,18 @@
           <t>TAGTA</t>
         </is>
       </c>
-      <c r="T236" t="n">
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U236" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U236" t="n">
+      <c r="V236" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V236" t="inlineStr">
+      <c r="W236" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -21966,7 +23026,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -22000,13 +23060,18 @@
           <t>TAGTAAAAATA</t>
         </is>
       </c>
-      <c r="T237" t="n">
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U237" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U237" t="n">
+      <c r="V237" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V237" t="inlineStr">
+      <c r="W237" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -22062,7 +23127,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -22096,13 +23161,18 @@
           <t>TAAAAATA</t>
         </is>
       </c>
-      <c r="T238" t="n">
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U238" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U238" t="n">
+      <c r="V238" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V238" t="inlineStr">
+      <c r="W238" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -22158,7 +23228,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -22192,13 +23262,18 @@
           <t>TAGTAAAAATACTA</t>
         </is>
       </c>
-      <c r="T239" t="n">
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U239" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U239" t="n">
+      <c r="V239" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V239" t="inlineStr">
+      <c r="W239" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -22254,7 +23329,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>0.2818</v>
+        <v>0.281</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -22288,13 +23363,18 @@
           <t>TACTA</t>
         </is>
       </c>
-      <c r="T240" t="n">
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U240" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U240" t="n">
+      <c r="V240" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V240" t="inlineStr">
+      <c r="W240" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -22350,7 +23430,7 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -22384,13 +23464,18 @@
           <t>TTAGTAAAAATACTAA</t>
         </is>
       </c>
-      <c r="T241" t="n">
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U241" t="n">
         <v>0.0009996001599360256</v>
       </c>
-      <c r="U241" t="n">
+      <c r="V241" t="n">
         <v>0.9990003998400639</v>
       </c>
-      <c r="V241" t="inlineStr">
+      <c r="W241" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -22446,7 +23531,7 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -22480,13 +23565,18 @@
           <t>TTAGTAA</t>
         </is>
       </c>
-      <c r="T242" t="n">
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U242" t="n">
         <v>0.7473010795681727</v>
       </c>
-      <c r="U242" t="n">
+      <c r="V242" t="n">
         <v>0.2526989204318273</v>
       </c>
-      <c r="V242" t="inlineStr">
+      <c r="W242" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -22542,7 +23632,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -22576,13 +23666,18 @@
           <t>TAGTAAAAATA</t>
         </is>
       </c>
-      <c r="T243" t="n">
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U243" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U243" t="n">
+      <c r="V243" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V243" t="inlineStr">
+      <c r="W243" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -22638,7 +23733,7 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -22672,13 +23767,18 @@
           <t>TAAAAATACTA</t>
         </is>
       </c>
-      <c r="T244" t="n">
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U244" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U244" t="n">
+      <c r="V244" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V244" t="inlineStr">
+      <c r="W244" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -22734,7 +23834,7 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>0.2539</v>
+        <v>0.252</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -22768,13 +23868,18 @@
           <t>TACTA</t>
         </is>
       </c>
-      <c r="T245" t="n">
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U245" t="n">
         <v>0.9996001599360256</v>
       </c>
-      <c r="U245" t="n">
+      <c r="V245" t="n">
         <v>0.0003998400639744215</v>
       </c>
-      <c r="V245" t="inlineStr">
+      <c r="W245" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -22830,7 +23935,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -22864,13 +23969,18 @@
           <t>CGAACAAAAACCGAACA</t>
         </is>
       </c>
-      <c r="T246" t="n">
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U246" t="n">
         <v>0.1105557776889244</v>
       </c>
-      <c r="U246" t="n">
+      <c r="V246" t="n">
         <v>0.8894442223110756</v>
       </c>
-      <c r="V246" t="inlineStr">
+      <c r="W246" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -22926,7 +24036,7 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -22960,13 +24070,18 @@
           <t>AAAAA</t>
         </is>
       </c>
-      <c r="T247" t="n">
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U247" t="n">
         <v>0.7842862854858057</v>
       </c>
-      <c r="U247" t="n">
+      <c r="V247" t="n">
         <v>0.2157137145141943</v>
       </c>
-      <c r="V247" t="inlineStr">
+      <c r="W247" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23022,7 +24137,7 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -23056,13 +24171,18 @@
           <t>AAAAA</t>
         </is>
       </c>
-      <c r="T248" t="n">
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U248" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="U248" t="n">
+      <c r="V248" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="V248" t="inlineStr">
+      <c r="W248" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23118,7 +24238,7 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -23152,13 +24272,18 @@
           <t>AACAAAAAC</t>
         </is>
       </c>
-      <c r="T249" t="n">
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U249" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="U249" t="n">
+      <c r="V249" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="V249" t="inlineStr">
+      <c r="W249" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23214,7 +24339,7 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -23248,13 +24373,18 @@
           <t>AACCGAAC</t>
         </is>
       </c>
-      <c r="T250" t="n">
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U250" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="U250" t="n">
+      <c r="V250" t="n">
         <v>0.0005997600959616323</v>
       </c>
-      <c r="V250" t="inlineStr">
+      <c r="W250" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23310,7 +24440,7 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -23344,13 +24474,18 @@
           <t>AACAA</t>
         </is>
       </c>
-      <c r="T251" t="n">
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U251" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U251" t="n">
+      <c r="V251" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V251" t="inlineStr">
+      <c r="W251" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23406,7 +24541,7 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -23440,13 +24575,18 @@
           <t>AACAAA</t>
         </is>
       </c>
-      <c r="T252" t="n">
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U252" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U252" t="n">
+      <c r="V252" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V252" t="inlineStr">
+      <c r="W252" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23502,7 +24642,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -23536,13 +24676,18 @@
           <t>AACAAAA</t>
         </is>
       </c>
-      <c r="T253" t="n">
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U253" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U253" t="n">
+      <c r="V253" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V253" t="inlineStr">
+      <c r="W253" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23598,7 +24743,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -23632,13 +24777,18 @@
           <t>AAAAA</t>
         </is>
       </c>
-      <c r="T254" t="n">
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U254" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U254" t="n">
+      <c r="V254" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V254" t="inlineStr">
+      <c r="W254" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23694,7 +24844,7 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -23728,13 +24878,18 @@
           <t>AAAAACCGAA</t>
         </is>
       </c>
-      <c r="T255" t="n">
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U255" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U255" t="n">
+      <c r="V255" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V255" t="inlineStr">
+      <c r="W255" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23790,7 +24945,7 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -23824,13 +24979,18 @@
           <t>AAAACCGAA</t>
         </is>
       </c>
-      <c r="T256" t="n">
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U256" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U256" t="n">
+      <c r="V256" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V256" t="inlineStr">
+      <c r="W256" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23886,7 +25046,7 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>0.4179</v>
+        <v>0.3701</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -23920,13 +25080,18 @@
           <t>AAACCGAA</t>
         </is>
       </c>
-      <c r="T257" t="n">
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U257" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="U257" t="n">
+      <c r="V257" t="n">
         <v>0.0001999200319872108</v>
       </c>
-      <c r="V257" t="inlineStr">
+      <c r="W257" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -23982,7 +25147,7 @@
         </is>
       </c>
       <c r="K258" t="n">
-        <v>0.2381</v>
+        <v>0.2875</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -24016,13 +25181,18 @@
           <t>CGAACAAAAACCG</t>
         </is>
       </c>
-      <c r="T258" t="n">
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U258" t="n">
         <v>0.7530987604958017</v>
       </c>
-      <c r="U258" t="n">
+      <c r="V258" t="n">
         <v>0.2469012395041983</v>
       </c>
-      <c r="V258" t="inlineStr">
+      <c r="W258" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -24078,7 +25248,7 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>0.2393</v>
+        <v>0.1931</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -24112,13 +25282,18 @@
           <t>GAACACGCGCAGAAC</t>
         </is>
       </c>
-      <c r="T259" t="n">
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U259" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="U259" t="n">
+      <c r="V259" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="V259" t="inlineStr">
+      <c r="W259" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -24170,7 +25345,7 @@
       </c>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -24188,15 +25363,16 @@
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
-      <c r="T260" t="n">
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="n">
         <v>1</v>
       </c>
-      <c r="U260" t="n">
+      <c r="V260" t="n">
         <v>0</v>
       </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -24246,7 +25422,7 @@
       </c>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="n">
-        <v>0.0613</v>
+        <v>0.0644</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -24264,15 +25440,16 @@
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr"/>
-      <c r="T261" t="n">
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="n">
         <v>1</v>
       </c>
-      <c r="U261" t="n">
+      <c r="V261" t="n">
         <v>0</v>
       </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -24322,7 +25499,7 @@
       </c>
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="n">
-        <v>0.1101</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -24340,15 +25517,16 @@
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr"/>
-      <c r="T262" t="n">
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="n">
         <v>1</v>
       </c>
-      <c r="U262" t="n">
+      <c r="V262" t="n">
         <v>0</v>
       </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -24402,7 +25580,7 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>0.2173</v>
+        <v>0.2618</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -24436,13 +25614,18 @@
           <t>TTTAATTATTGTT</t>
         </is>
       </c>
-      <c r="T263" t="n">
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U263" t="n">
         <v>0.08756497401039584</v>
       </c>
-      <c r="U263" t="n">
+      <c r="V263" t="n">
         <v>0.9124350259896041</v>
       </c>
-      <c r="V263" t="inlineStr">
+      <c r="W263" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -24498,7 +25681,7 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>0.2173</v>
+        <v>0.2618</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -24532,13 +25715,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T264" t="n">
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U264" t="n">
         <v>0.2786885245901639</v>
       </c>
-      <c r="U264" t="n">
+      <c r="V264" t="n">
         <v>0.7213114754098361</v>
       </c>
-      <c r="V264" t="inlineStr">
+      <c r="W264" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -24594,7 +25782,7 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>0.2641</v>
+        <v>0.218</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -24628,13 +25816,18 @@
           <t>AATTATTGTTT</t>
         </is>
       </c>
-      <c r="T265" t="n">
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U265" t="n">
         <v>0.2544982007197121</v>
       </c>
-      <c r="U265" t="n">
+      <c r="V265" t="n">
         <v>0.7455017992802879</v>
       </c>
-      <c r="V265" t="inlineStr">
+      <c r="W265" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -24690,7 +25883,7 @@
         </is>
       </c>
       <c r="K266" t="n">
-        <v>0.2464</v>
+        <v>0.2815</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -24724,13 +25917,18 @@
           <t>TTTATAATTTGTT</t>
         </is>
       </c>
-      <c r="T266" t="n">
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U266" t="n">
         <v>0.08696521391443422</v>
       </c>
-      <c r="U266" t="n">
+      <c r="V266" t="n">
         <v>0.9130347860855658</v>
       </c>
-      <c r="V266" t="inlineStr">
+      <c r="W266" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -24786,7 +25984,7 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>0.2464</v>
+        <v>0.2815</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -24820,13 +26018,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T267" t="n">
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U267" t="n">
         <v>0.2109156337465014</v>
       </c>
-      <c r="U267" t="n">
+      <c r="V267" t="n">
         <v>0.7890843662534985</v>
       </c>
-      <c r="V267" t="inlineStr">
+      <c r="W267" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -24878,7 +26081,7 @@
       </c>
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="n">
-        <v>0.1022</v>
+        <v>0.0725</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -24896,15 +26099,16 @@
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr"/>
-      <c r="T268" t="n">
+      <c r="T268" t="inlineStr"/>
+      <c r="U268" t="n">
         <v>1</v>
       </c>
-      <c r="U268" t="n">
+      <c r="V268" t="n">
         <v>0</v>
       </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -24958,7 +26162,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>0.1937</v>
+        <v>0.195</v>
       </c>
       <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr"/>
@@ -24988,13 +26192,18 @@
           <t>AACGCTCCCGAAAC</t>
         </is>
       </c>
-      <c r="T269" t="n">
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U269" t="n">
         <v>0.001199520191923231</v>
       </c>
-      <c r="U269" t="n">
+      <c r="V269" t="n">
         <v>0.9988004798080767</v>
       </c>
-      <c r="V269" t="inlineStr">
+      <c r="W269" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -25046,7 +26255,7 @@
       </c>
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="n">
-        <v>0.0707</v>
+        <v>0.1185</v>
       </c>
       <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
@@ -25060,15 +26269,16 @@
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr"/>
-      <c r="T270" t="n">
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="n">
         <v>1</v>
       </c>
-      <c r="U270" t="n">
+      <c r="V270" t="n">
         <v>0</v>
       </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -25122,7 +26332,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>0.3059</v>
+        <v>0.2507</v>
       </c>
       <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr"/>
@@ -25152,13 +26362,18 @@
           <t>GTTAAAAAAATGTTA</t>
         </is>
       </c>
-      <c r="T271" t="n">
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U271" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U271" t="n">
+      <c r="V271" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V271" t="inlineStr">
+      <c r="W271" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -25214,7 +26429,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>0.2578</v>
+        <v>0.2927</v>
       </c>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr"/>
@@ -25244,13 +26459,18 @@
           <t>TAAAAAAATGTTA</t>
         </is>
       </c>
-      <c r="T272" t="n">
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U272" t="n">
         <v>0.1343462614954019</v>
       </c>
-      <c r="U272" t="n">
+      <c r="V272" t="n">
         <v>0.8656537385045981</v>
       </c>
-      <c r="V272" t="inlineStr">
+      <c r="W272" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -25302,7 +26522,7 @@
       </c>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="n">
-        <v>0.1151</v>
+        <v>0.0638</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -25320,15 +26540,16 @@
       <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr"/>
       <c r="S273" t="inlineStr"/>
-      <c r="T273" t="n">
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="n">
         <v>1</v>
       </c>
-      <c r="U273" t="n">
+      <c r="V273" t="n">
         <v>0</v>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -25378,7 +26599,7 @@
       </c>
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="n">
-        <v>0.064</v>
+        <v>0.0659</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -25396,15 +26617,16 @@
       <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr"/>
-      <c r="T274" t="n">
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="n">
         <v>1</v>
       </c>
-      <c r="U274" t="n">
+      <c r="V274" t="n">
         <v>0</v>
       </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -25458,7 +26680,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>0.3106</v>
+        <v>0.3162</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -25492,13 +26714,18 @@
           <t>TTAATGTCCGGTTAA</t>
         </is>
       </c>
-      <c r="T275" t="n">
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U275" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U275" t="n">
+      <c r="V275" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V275" t="inlineStr">
+      <c r="W275" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -25554,7 +26781,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>0.2557</v>
+        <v>0.2988</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -25588,13 +26815,18 @@
           <t>TTAATGTCCGGTTAA</t>
         </is>
       </c>
-      <c r="T276" t="n">
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U276" t="n">
         <v>0.1487405037984806</v>
       </c>
-      <c r="U276" t="n">
+      <c r="V276" t="n">
         <v>0.8512594962015194</v>
       </c>
-      <c r="V276" t="inlineStr">
+      <c r="W276" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -25650,7 +26882,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr"/>
@@ -25680,13 +26912,18 @@
           <t>TTTAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T277" t="n">
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U277" t="n">
         <v>0.0005997600959616154</v>
       </c>
-      <c r="U277" t="n">
+      <c r="V277" t="n">
         <v>0.9994002399040384</v>
       </c>
-      <c r="V277" t="inlineStr">
+      <c r="W277" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -25742,7 +26979,7 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
@@ -25772,13 +27009,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T278" t="n">
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U278" t="n">
         <v>0.2389044382247101</v>
       </c>
-      <c r="U278" t="n">
+      <c r="V278" t="n">
         <v>0.7610955617752899</v>
       </c>
-      <c r="V278" t="inlineStr">
+      <c r="W278" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -25834,7 +27076,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr"/>
@@ -25864,13 +27106,18 @@
           <t>TTAGATTTTGTT</t>
         </is>
       </c>
-      <c r="T279" t="n">
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U279" t="n">
         <v>0.2131147540983606</v>
       </c>
-      <c r="U279" t="n">
+      <c r="V279" t="n">
         <v>0.7868852459016393</v>
       </c>
-      <c r="V279" t="inlineStr">
+      <c r="W279" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -25926,7 +27173,7 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
@@ -25956,13 +27203,18 @@
           <t>TTTAGATTTTGTTT</t>
         </is>
       </c>
-      <c r="T280" t="n">
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U280" t="n">
         <v>0.1933226709316274</v>
       </c>
-      <c r="U280" t="n">
+      <c r="V280" t="n">
         <v>0.8066773290683726</v>
       </c>
-      <c r="V280" t="inlineStr">
+      <c r="W280" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -26018,7 +27270,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>0.3266</v>
+        <v>0.2789</v>
       </c>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
@@ -26048,13 +27300,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T281" t="n">
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U281" t="n">
         <v>0.1629348260695722</v>
       </c>
-      <c r="U281" t="n">
+      <c r="V281" t="n">
         <v>0.8370651739304278</v>
       </c>
-      <c r="V281" t="inlineStr">
+      <c r="W281" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -26110,7 +27367,7 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>0.2761</v>
+        <v>0.3274</v>
       </c>
       <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr"/>
@@ -26140,13 +27397,18 @@
           <t>TAGATTTTGTTTA</t>
         </is>
       </c>
-      <c r="T282" t="n">
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U282" t="n">
         <v>0.1971211515393843</v>
       </c>
-      <c r="U282" t="n">
+      <c r="V282" t="n">
         <v>0.8028788484606157</v>
       </c>
-      <c r="V282" t="inlineStr">
+      <c r="W282" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -26202,7 +27464,7 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>0.275</v>
+        <v>0.278</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -26236,13 +27498,18 @@
           <t>GTTTATATTTTGTT</t>
         </is>
       </c>
-      <c r="T283" t="n">
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U283" t="n">
         <v>0.00819672131147541</v>
       </c>
-      <c r="U283" t="n">
+      <c r="V283" t="n">
         <v>0.9918032786885246</v>
       </c>
-      <c r="V283" t="inlineStr">
+      <c r="W283" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -26294,7 +27561,7 @@
       </c>
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="n">
-        <v>0.1244</v>
+        <v>0.1354</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -26312,15 +27579,16 @@
       <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr"/>
       <c r="S284" t="inlineStr"/>
-      <c r="T284" t="n">
+      <c r="T284" t="inlineStr"/>
+      <c r="U284" t="n">
         <v>1</v>
       </c>
-      <c r="U284" t="n">
+      <c r="V284" t="n">
         <v>0</v>
       </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -26374,7 +27642,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>0.2061</v>
+        <v>0.2055</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -26408,13 +27676,18 @@
           <t>TTT</t>
         </is>
       </c>
-      <c r="T285" t="n">
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U285" t="n">
         <v>0.2213114754098361</v>
       </c>
-      <c r="U285" t="n">
+      <c r="V285" t="n">
         <v>0.7786885245901639</v>
       </c>
-      <c r="V285" t="inlineStr">
+      <c r="W285" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -26470,7 +27743,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>0.2061</v>
+        <v>0.2055</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -26504,13 +27777,18 @@
           <t>TTTAGGGTTTGTT</t>
         </is>
       </c>
-      <c r="T286" t="n">
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U286" t="n">
         <v>0.4096361455417833</v>
       </c>
-      <c r="U286" t="n">
+      <c r="V286" t="n">
         <v>0.5903638544582167</v>
       </c>
-      <c r="V286" t="inlineStr">
+      <c r="W286" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -26566,7 +27844,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>0.2061</v>
+        <v>0.2055</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -26600,13 +27878,18 @@
           <t>TTAGGGTTTGTT</t>
         </is>
       </c>
-      <c r="T287" t="n">
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U287" t="n">
         <v>0.2213114754098361</v>
       </c>
-      <c r="U287" t="n">
+      <c r="V287" t="n">
         <v>0.7786885245901639</v>
       </c>
-      <c r="V287" t="inlineStr">
+      <c r="W287" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -26658,7 +27941,7 @@
       </c>
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="n">
-        <v>0.066</v>
+        <v>0.119</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -26676,15 +27959,16 @@
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr"/>
-      <c r="T288" t="n">
+      <c r="T288" t="inlineStr"/>
+      <c r="U288" t="n">
         <v>1</v>
       </c>
-      <c r="U288" t="n">
+      <c r="V288" t="n">
         <v>0</v>
       </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -26738,7 +28022,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>0.2005</v>
+        <v>0.2037</v>
       </c>
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr"/>
@@ -26768,13 +28052,18 @@
           <t>GTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T289" t="n">
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U289" t="n">
         <v>0.0001999200319872051</v>
       </c>
-      <c r="U289" t="n">
+      <c r="V289" t="n">
         <v>0.9998000799680128</v>
       </c>
-      <c r="V289" t="inlineStr">
+      <c r="W289" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -26830,7 +28119,7 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>0.2028</v>
+        <v>0.2539</v>
       </c>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
@@ -26860,13 +28149,18 @@
           <t>TGTCA</t>
         </is>
       </c>
-      <c r="T290" t="n">
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U290" t="n">
         <v>0.1671331467413035</v>
       </c>
-      <c r="U290" t="n">
+      <c r="V290" t="n">
         <v>0.8328668532586965</v>
       </c>
-      <c r="V290" t="inlineStr">
+      <c r="W290" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -26922,7 +28216,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>0.2028</v>
+        <v>0.2539</v>
       </c>
       <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr"/>
@@ -26952,13 +28246,18 @@
           <t>TGTCACACAACTGTCA</t>
         </is>
       </c>
-      <c r="T291" t="n">
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U291" t="n">
         <v>0.1143542582966813</v>
       </c>
-      <c r="U291" t="n">
+      <c r="V291" t="n">
         <v>0.8856457417033187</v>
       </c>
-      <c r="V291" t="inlineStr">
+      <c r="W291" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -27010,7 +28309,7 @@
       </c>
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="n">
-        <v>0.1127</v>
+        <v>0.0736</v>
       </c>
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
@@ -27024,15 +28323,16 @@
       <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr"/>
-      <c r="T292" t="n">
+      <c r="T292" t="inlineStr"/>
+      <c r="U292" t="n">
         <v>1</v>
       </c>
-      <c r="U292" t="n">
+      <c r="V292" t="n">
         <v>0</v>
       </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>Weak agree</t>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -27086,7 +28386,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>0.2389</v>
+        <v>0.2377</v>
       </c>
       <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr"/>
@@ -27116,13 +28416,18 @@
           <t>TGTAACA</t>
         </is>
       </c>
-      <c r="T293" t="n">
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U293" t="n">
         <v>0.01019592163134746</v>
       </c>
-      <c r="U293" t="n">
+      <c r="V293" t="n">
         <v>0.9898040783686526</v>
       </c>
-      <c r="V293" t="inlineStr">
+      <c r="W293" t="inlineStr">
         <is>
           <t>Strong disagree</t>
         </is>
@@ -27178,7 +28483,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>0.2926</v>
+        <v>0.3038</v>
       </c>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
@@ -27208,13 +28513,18 @@
           <t>TTACTT</t>
         </is>
       </c>
-      <c r="T294" t="n">
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U294" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="U294" t="n">
+      <c r="V294" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="V294" t="inlineStr">
+      <c r="W294" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -27270,7 +28580,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>0.2926</v>
+        <v>0.3038</v>
       </c>
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
@@ -27300,13 +28610,18 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="T295" t="n">
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U295" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="U295" t="n">
+      <c r="V295" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="V295" t="inlineStr">
+      <c r="W295" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -27362,7 +28677,7 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>0.2926</v>
+        <v>0.3038</v>
       </c>
       <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr"/>
@@ -27392,13 +28707,18 @@
           <t>TTACTTACAAAATGTT</t>
         </is>
       </c>
-      <c r="T296" t="n">
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U296" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="U296" t="n">
+      <c r="V296" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="V296" t="inlineStr">
+      <c r="W296" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -27454,7 +28774,7 @@
         </is>
       </c>
       <c r="K297" t="n">
-        <v>0.2926</v>
+        <v>0.3038</v>
       </c>
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
@@ -27484,13 +28804,18 @@
           <t>TTACAAAATGTT</t>
         </is>
       </c>
-      <c r="T297" t="n">
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U297" t="n">
         <v>0.9406237504998001</v>
       </c>
-      <c r="U297" t="n">
+      <c r="V297" t="n">
         <v>0.05937624950019993</v>
       </c>
-      <c r="V297" t="inlineStr">
+      <c r="W297" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -27546,7 +28871,7 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
@@ -27576,13 +28901,18 @@
           <t>TTACTTACAAA</t>
         </is>
       </c>
-      <c r="T298" t="n">
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U298" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U298" t="n">
+      <c r="V298" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V298" t="inlineStr">
+      <c r="W298" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -27638,7 +28968,7 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
@@ -27668,13 +28998,18 @@
           <t>TTACAAA</t>
         </is>
       </c>
-      <c r="T299" t="n">
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U299" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U299" t="n">
+      <c r="V299" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V299" t="inlineStr">
+      <c r="W299" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -27730,7 +29065,7 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
@@ -27760,13 +29095,18 @@
           <t>TTACTTACAAAA</t>
         </is>
       </c>
-      <c r="T300" t="n">
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U300" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U300" t="n">
+      <c r="V300" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V300" t="inlineStr">
+      <c r="W300" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -27822,7 +29162,7 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr"/>
@@ -27852,13 +29192,18 @@
           <t>TTACAAAA</t>
         </is>
       </c>
-      <c r="T301" t="n">
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U301" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U301" t="n">
+      <c r="V301" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V301" t="inlineStr">
+      <c r="W301" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -27914,7 +29259,7 @@
         </is>
       </c>
       <c r="K302" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
@@ -27944,13 +29289,18 @@
           <t>AAATGTT</t>
         </is>
       </c>
-      <c r="T302" t="n">
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U302" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U302" t="n">
+      <c r="V302" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V302" t="inlineStr">
+      <c r="W302" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -28006,7 +29356,7 @@
         </is>
       </c>
       <c r="K303" t="n">
-        <v>0.237</v>
+        <v>0.2426</v>
       </c>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
@@ -28036,13 +29386,18 @@
           <t>AATGTT</t>
         </is>
       </c>
-      <c r="T303" t="n">
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U303" t="n">
         <v>0.7237105157936825</v>
       </c>
-      <c r="U303" t="n">
+      <c r="V303" t="n">
         <v>0.2762894842063175</v>
       </c>
-      <c r="V303" t="inlineStr">
+      <c r="W303" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -28098,7 +29453,7 @@
         </is>
       </c>
       <c r="K304" t="n">
-        <v>0.2348</v>
+        <v>0.2402</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -28132,13 +29487,18 @@
           <t>TATCACCCCGGATA</t>
         </is>
       </c>
-      <c r="T304" t="n">
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U304" t="n">
         <v>0.1117552978808477</v>
       </c>
-      <c r="U304" t="n">
+      <c r="V304" t="n">
         <v>0.8882447021191523</v>
       </c>
-      <c r="V304" t="inlineStr">
+      <c r="W304" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -28194,7 +29554,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>0.196</v>
+        <v>0.1947</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -28228,13 +29588,18 @@
           <t>GTATCACCCCGGATAC</t>
         </is>
       </c>
-      <c r="T305" t="n">
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U305" t="n">
         <v>0.006797281087564974</v>
       </c>
-      <c r="U305" t="n">
+      <c r="V305" t="n">
         <v>0.9932027189124351</v>
       </c>
-      <c r="V305" t="inlineStr">
+      <c r="W305" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -28290,7 +29655,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>0.2433</v>
+        <v>0.2615</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -28324,13 +29689,18 @@
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="T306" t="n">
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U306" t="n">
         <v>0.004198320671731308</v>
       </c>
-      <c r="U306" t="n">
+      <c r="V306" t="n">
         <v>0.9958016793282687</v>
       </c>
-      <c r="V306" t="inlineStr">
+      <c r="W306" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -28386,7 +29756,7 @@
         </is>
       </c>
       <c r="K307" t="n">
-        <v>0.2433</v>
+        <v>0.2615</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -28420,13 +29790,18 @@
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="T307" t="n">
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U307" t="n">
         <v>0.04278288684526189</v>
       </c>
-      <c r="U307" t="n">
+      <c r="V307" t="n">
         <v>0.9572171131547381</v>
       </c>
-      <c r="V307" t="inlineStr">
+      <c r="W307" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -28482,7 +29857,7 @@
         </is>
       </c>
       <c r="K308" t="n">
-        <v>0.2433</v>
+        <v>0.2615</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -28516,13 +29891,18 @@
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="T308" t="n">
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U308" t="n">
         <v>0.4920031987205118</v>
       </c>
-      <c r="U308" t="n">
+      <c r="V308" t="n">
         <v>0.5079968012794882</v>
       </c>
-      <c r="V308" t="inlineStr">
+      <c r="W308" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -28574,7 +29954,7 @@
       </c>
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="n">
-        <v>0.0646</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -28592,15 +29972,16 @@
       <c r="Q309" t="inlineStr"/>
       <c r="R309" t="inlineStr"/>
       <c r="S309" t="inlineStr"/>
-      <c r="T309" t="n">
+      <c r="T309" t="inlineStr"/>
+      <c r="U309" t="n">
         <v>1</v>
       </c>
-      <c r="U309" t="n">
+      <c r="V309" t="n">
         <v>0</v>
       </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -28654,7 +30035,7 @@
         </is>
       </c>
       <c r="K310" t="n">
-        <v>0.1887</v>
+        <v>0.1941</v>
       </c>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
@@ -28684,13 +30065,18 @@
           <t>GTTAATTAAATGT</t>
         </is>
       </c>
-      <c r="T310" t="n">
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U310" t="n">
         <v>0.07976809276289484</v>
       </c>
-      <c r="U310" t="n">
+      <c r="V310" t="n">
         <v>0.9202319072371051</v>
       </c>
-      <c r="V310" t="inlineStr">
+      <c r="W310" t="inlineStr">
         <is>
           <t>Weak agree</t>
         </is>
@@ -28742,7 +30128,7 @@
       </c>
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="n">
-        <v>0.1411</v>
+        <v>0.1104</v>
       </c>
       <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
@@ -28756,15 +30142,16 @@
       <c r="Q311" t="inlineStr"/>
       <c r="R311" t="inlineStr"/>
       <c r="S311" t="inlineStr"/>
-      <c r="T311" t="n">
+      <c r="T311" t="inlineStr"/>
+      <c r="U311" t="n">
         <v>1</v>
       </c>
-      <c r="U311" t="n">
+      <c r="V311" t="n">
         <v>0</v>
       </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>Weak disagree</t>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>No candidates found</t>
         </is>
       </c>
     </row>
@@ -28818,7 +30205,7 @@
         </is>
       </c>
       <c r="K312" t="n">
-        <v>0.2318</v>
+        <v>0.2315</v>
       </c>
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr"/>
@@ -28848,13 +30235,18 @@
           <t>TTCATAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T312" t="n">
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
+      <c r="U312" t="n">
         <v>0.002199120351859256</v>
       </c>
-      <c r="U312" t="n">
+      <c r="V312" t="n">
         <v>0.9978008796481408</v>
       </c>
-      <c r="V312" t="inlineStr">
+      <c r="W312" t="inlineStr">
         <is>
           <t>Strong agree</t>
         </is>
@@ -28910,7 +30302,7 @@
         </is>
       </c>
       <c r="K313" t="n">
-        <v>0.2697</v>
+        <v>0.229</v>
       </c>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
@@ -28940,13 +30332,18 @@
           <t>ATAATTTTTCAT</t>
         </is>
       </c>
-      <c r="T313" t="n">
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U313" t="n">
         <v>0.9822071171531388</v>
       </c>
-      <c r="U313" t="n">
+      <c r="V313" t="n">
         <v>0.0177928828468612</v>
       </c>
-      <c r="V313" t="inlineStr">
+      <c r="W313" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
@@ -29002,7 +30399,7 @@
         </is>
       </c>
       <c r="K314" t="n">
-        <v>0.2697</v>
+        <v>0.229</v>
       </c>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
@@ -29032,13 +30429,18 @@
           <t>TAATTTTTCATA</t>
         </is>
       </c>
-      <c r="T314" t="n">
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="U314" t="n">
         <v>0.9822071171531388</v>
       </c>
-      <c r="U314" t="n">
+      <c r="V314" t="n">
         <v>0.0177928828468612</v>
       </c>
-      <c r="V314" t="inlineStr">
+      <c r="W314" t="inlineStr">
         <is>
           <t>Weak disagree</t>
         </is>
